--- a/pacjenci/GRZEGORZ JARECKI.xlsx
+++ b/pacjenci/GRZEGORZ JARECKI.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/GRZEGORZ JARECKI.xlsx
+++ b/pacjenci/GRZEGORZ JARECKI.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.07.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena zaawansowania choroby przed rozpoczęciem leczenia.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 83mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>oraz klatka piersiowa: Aktywne metabolicznie węzły chłonne: - grupy 2A  po stronie lewej średnicy wg PET 16mm, SUV max 5,8, - grupy 3 po stronie prawej średnicy wg PET 18mm, SUV max 6,4 - podostrogowe średnicy wg PET 43mm, SUV max 8,9, - nad i podobojczykowe prawe średnicy wg PET 26mm, SUV max 8,7, - przyaortalny po stronie lewej na wysokości trzonu kręgu Th5 średnicy wg PET 20mm, SUV max 6,6, - zachyłku przeponowo-sercowym lewym wielkości wg PET 45x23mm, SUV max 9,9. Heterogenna metabolicznie masa miękkotkankowa w śródpiersiu górnym przednim łącząca się z węzłami chłonnymi szyi grupy 3, 4 i 5 po stronie lewej i położonymi lewobocznie od łuku aorty wielkości wg PET 160x71x182mm, SUV max do 11,7-   zmiana przemieszcza tchawice i tarczycę na stronę prawą.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W przyleganiu do zmiany w śródpiersiu, w płacie środkowym i górnym  widoczny dyskretny obszar mlecznej szyby i podrysowane linie przegrodowe.  Niewielka zmiana naciekowo-niedodmowa nadprzeponowo po prawej.  Drobne, guzkowe nawarstwienia opłucnej szerokości do 2mm w przyleganiu do segmentów grzbietowych płatów dolnych.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Spłycenie fizjologicznych krzywizn kregosłupa.  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po jednej stronie przepony.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>11.7</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>11.10.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Wczesna ocena odpowiedzi po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 87mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Ok. 11mm torbiel w kości szczękowej, pośrodkowo. Ok. 13mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim i środkowym pośrodkowo i po stronie lewej, o orientacyjnej wielkości 76x45x85mm, z przemieszczeniem tchawicy, tarczycy i struktur śródpiersia górnego na stronę prawą - dokładna ocena wielkości masy możliwa w badaniu TK KLP z kontrastem dożylnym. Pojedyncze nieaktywne metabolicznie węzły chłonne śródpiersiowe i przytchawicze wielkości do 26x30mm. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz prawego. Niewielka zmiana naciekowo-niedodmowa nadprzeponowo po prawej.  Drobne przylegające do siebie zmiany guzkowe w segmentach grzbietowych płatów dolnych obu płuc, wielkości do 9mm [większe po stronie lewej]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzenie metaboliczne śledziony, SUV max do 4,1- związane ze stosowanym leczeniem? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>14.02.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Stan po 2 cyklach ABVD i 6 cyklach AVD. Ocena zaawansowania choroby. Podwyższone OB.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  54min od podania 18F-FDG. Glikemia: 89mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie głosowym SUV max 4,3- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Ok. 10 mm torbiel w kości szczękowej, pośrodkowo, z wyraźnym ścieńczeniem blaszki zewn. - dokładna ocena możliwa w badaniu celowanym TK. Ok. 18 mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej oraz bardzo drobne w prawej.  Klatka piersiowa: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim i środkowym pośrodkowo i po stronie lewej, o orientacyjnej wielkości 76x41x79 mm, z przemieszczeniem tchawicy, tarczycy i struktur śródpiersia górnego na stronę prawą - dokładna ocena wielkości masy możliwa w badaniu TK KLP z kontrastem dożylnym. Pojedyncze nieaktywne metabolicznie węzły chłonne śródpiersiowe i przytchawicze wielkości do 18x25 mm. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz prawego. Niewielka zmiana niedodmowo-włóknista nadprzeponowo po prawej.  Drobne przylegające do siebie zmiany guzkowe w segmentach grzbietowych płatów dolnych obu płuc, wielkości do 7mm [większe po stronie lewej]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.  Układ kostny: Aktywny metabolicznie obszar w górno- lewobocznej części rękojeści mostka, średnicy 9 mm wg PET SUV max 3,9. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie obszaru w rękojeści mostka po stronie lewej - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.3</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>18.04.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina, grade 2. Ocena po zakończeniu chemioterapii. W poprzednim badaniu PET -aktywny metabolicznie obszar w rękojeści mostka po stronie lewej - kontrola.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  58 min od podania 18F-FDG. Glikemia: 99mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetrycznie wzmożony metabolizm FDG w  topografii ujść obu trąbek słuchowych [zwłaszcza lewej] SUV max do 3,3 oraz w strukturach pierścienia Waldeyera SUV max do 7,9 - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Ok. 12 mm torbiel w kości szczękowej, pośrodkowo, z wyraźnym ścieńczeniem blaszki zewn. - dokładna ocena możliwa w badaniu celowanym TK. Ok. 19 mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej oraz bardzo drobne w prawej.  Klatka piersiowa: Masa miękkotkankowa w śródpiersiu przednim i środkowym pośrodkowo i po stronie lewej, o orientacyjnej wielkości 63x37x64 mm SUV max do 2,3 [Im CT 331] - dokładna ocena wielkości masy możliwa w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze nieaktywne metabolicznie węzły chłonne śródpiersiowe i przytchawicze wielkości do 14 mm. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz prawego. Niewielka zmiana niedodmowo-włóknista nadprzeponowo po prawej.  Niewielkie zmiany miąższowo-włókniste obwodowo w segm. 9/10 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niejednorodna struktura rękojeści mostka, zwłaszcza pośrodkowo. Wydatna wyspa kostna w prawej kości łonowej. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w mięśniu podłopatkowym lewym SUV max 3,7- w pierwszej kolejności zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego. Masa miękkotkankowa w śródpiersiu do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>7.9</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/GRZEGORZ JARECKI.xlsx
+++ b/pacjenci/GRZEGORZ JARECKI.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 83mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>oraz klatka piersiowa: Aktywne metabolicznie węzły chłonne: - grupy 2A  po stronie lewej średnicy wg PET 16mm, SUV max 5,8, - grupy 3 po stronie prawej średnicy wg PET 18mm, SUV max 6,4 - podostrogowe średnicy wg PET 43mm, SUV max 8,9, - nad i podobojczykowe prawe średnicy wg PET 26mm, SUV max 8,7, - przyaortalny po stronie lewej na wysokości trzonu kręgu Th5 średnicy wg PET 20mm, SUV max 6,6, - zachyłku przeponowo-sercowym lewym wielkości wg PET 45x23mm, SUV max 9,9. Heterogenna metabolicznie masa miękkotkankowa w śródpiersiu górnym przednim łącząca się z węzłami chłonnymi szyi grupy 3, 4 i 5 po stronie lewej i położonymi lewobocznie od łuku aorty wielkości wg PET 160x71x182mm, SUV max do 11,7-   zmiana przemieszcza tchawice i tarczycę na stronę prawą.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W przyleganiu do zmiany w śródpiersiu, w płacie środkowym i górnym  widoczny dyskretny obszar mlecznej szyby i podrysowane linie przegrodowe.  Niewielka zmiana naciekowo-niedodmowa nadprzeponowo po prawej.  Drobne, guzkowe nawarstwienia opłucnej szerokości do 2mm w przyleganiu do segmentów grzbietowych płatów dolnych.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Spłycenie fizjologicznych krzywizn kregosłupa.  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Spłycenie fizjologicznych krzywizn kregosłupa.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po jednej stronie przepony.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>11.7</v>
       </c>
     </row>
@@ -502,20 +544,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 87mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Ok. 11mm torbiel w kości szczękowej, pośrodkowo. Ok. 13mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim i środkowym pośrodkowo i po stronie lewej, o orientacyjnej wielkości 76x45x85mm, z przemieszczeniem tchawicy, tarczycy i struktur śródpiersia górnego na stronę prawą - dokładna ocena wielkości masy możliwa w badaniu TK KLP z kontrastem dożylnym. Pojedyncze nieaktywne metabolicznie węzły chłonne śródpiersiowe i przytchawicze wielkości do 26x30mm. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz prawego. Niewielka zmiana naciekowo-niedodmowa nadprzeponowo po prawej.  Drobne przylegające do siebie zmiany guzkowe w segmentach grzbietowych płatów dolnych obu płuc, wielkości do 9mm [większe po stronie lewej]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzenie metaboliczne śledziony, SUV max do 4,1- związane ze stosowanym leczeniem? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 2,6; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne śledziony, SUV max do 4,1- związane ze stosowanym leczeniem? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w układzie kostnym - w pierwszej kolejności związany ze stosowanym leczeniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -535,20 +594,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  54min od podania 18F-FDG. Glikemia: 89mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Asymetrycznie wzmożony metabolizm FDG w prawym fałdzie głosowym SUV max 4,3- do kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Ok. 10 mm torbiel w kości szczękowej, pośrodkowo, z wyraźnym ścieńczeniem blaszki zewn. - dokładna ocena możliwa w badaniu celowanym TK. Ok. 18 mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej oraz bardzo drobne w prawej.  Klatka piersiowa: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masa miękkotkankowa w śródpiersiu przednim i środkowym pośrodkowo i po stronie lewej, o orientacyjnej wielkości 76x41x79 mm, z przemieszczeniem tchawicy, tarczycy i struktur śródpiersia górnego na stronę prawą - dokładna ocena wielkości masy możliwa w badaniu TK KLP z kontrastem dożylnym. Pojedyncze nieaktywne metabolicznie węzły chłonne śródpiersiowe i przytchawicze wielkości do 18x25 mm. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz prawego. Niewielka zmiana niedodmowo-włóknista nadprzeponowo po prawej.  Drobne przylegające do siebie zmiany guzkowe w segmentach grzbietowych płatów dolnych obu płuc, wielkości do 7mm [większe po stronie lewej]. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.  Układ kostny: Aktywny metabolicznie obszar w górno- lewobocznej części rękojeści mostka, średnicy 9 mm wg PET SUV max 3,9. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>89</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Wątroba powiększona. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w górno- lewobocznej części rękojeści mostka, średnicy 9 mm wg PET SUV max 3,9. Poza tym niejednorodny metabolizm FDG w układzie kostnym objętym badaniem. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie obszaru w rękojeści mostka po stronie lewej - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -568,20 +644,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  58 min od podania 18F-FDG. Glikemia: 99mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożony metabolizm FDG w  topografii ujść obu trąbek słuchowych [zwłaszcza lewej] SUV max do 3,3 oraz w strukturach pierścienia Waldeyera SUV max do 7,9 - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja zatok czołowych, zwłaszcza prawej. Ok. 12 mm torbiel w kości szczękowej, pośrodkowo, z wyraźnym ścieńczeniem blaszki zewn. - dokładna ocena możliwa w badaniu celowanym TK. Ok. 19 mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej oraz bardzo drobne w prawej.  Klatka piersiowa: Masa miękkotkankowa w śródpiersiu przednim i środkowym pośrodkowo i po stronie lewej, o orientacyjnej wielkości 63x37x64 mm SUV max do 2,3 [Im CT 331] - dokładna ocena wielkości masy możliwa w badaniu TK KLP z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze nieaktywne metabolicznie węzły chłonne śródpiersiowe i przytchawicze wielkości do 14 mm. Drobne zmiany włókniste w szczytach obu płuc. Niewielkie zmiany włókniste przyśródpiersiowo w płacie górnym płuca lewego oraz prawego. Niewielka zmiana niedodmowo-włóknista nadprzeponowo po prawej.  Niewielkie zmiany miąższowo-włókniste obwodowo w segm. 9/10 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niejednorodna struktura rękojeści mostka, zwłaszcza pośrodkowo. Wydatna wyspa kostna w prawej kości łonowej. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w mięśniu podłopatkowym lewym SUV max 3,7- w pierwszej kolejności zmiany odczynowo-przeciążeniowe.  Wartości referencyjne: MBPS SUVmax do 1,9; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 7mm flebolit lub uwapniony węzeł chłonny w miednicy mniejszej po stronie przednio-lewobocznej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Niejednorodna struktura rękojeści mostka, zwłaszcza pośrodkowo. Wydatna wyspa kostna w prawej kości łonowej. Spłycenie fizjologicznych krzywizn kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym odcinku kręgosłupa piersiowego. Hemilumbalizacja kręgu S1, z dyskopatią na poziomie S1/S2. Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w mięśniu podłopatkowym lewym SUV max 3,7- w pierwszej kolejności zmiany odczynowo-przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego. Masa miękkotkankowa w śródpiersiu do dalszej kontroli. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>7.9</v>
       </c>
     </row>
